--- a/data/excel/avisos_trabajo.xlsx
+++ b/data/excel/avisos_trabajo.xlsx
@@ -104,6 +104,72 @@
   </x:si>
   <x:si>
     <x:t>Observaciones</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AV-000001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aprobado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ApoyoOperacional</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAE_AND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRUEBA-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prueba de hu 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Media</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1dc348ae-ab97-4182-a1e4-b29d684dde2a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-30T00:00:00.0000000Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T19:40:08.4718108Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConRestriccion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T19:44:04.7299442Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aviso creado en CMMS | Aprobacion: prueba</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AV-000002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Creado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Falla</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prueba de activo no disponible</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T00:00:00.0000000Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T19:45:29.2340779Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SinDetencion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aviso creado en CMMS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -469,29 +535,28 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AD1"/>
+  <x:dimension ref="A1:AD3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7.567768" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.710625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="12.710625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="12.853482" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="7.996339" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="11.139196" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="12.853482" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28.710625" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="9.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="9.282054" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="37.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="13.996339" style="0" customWidth="1"/>
+    <x:col min="14" max="15" width="28.282054" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="15.710625" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="12.424911" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="20" max="20" width="15.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="37.996339" style="0" customWidth="1"/>
+    <x:col min="20" max="20" width="28.282054" style="0" customWidth="1"/>
     <x:col min="21" max="21" width="13.853482" style="0" customWidth="1"/>
     <x:col min="22" max="22" width="15.853482" style="0" customWidth="1"/>
     <x:col min="23" max="23" width="14.996339" style="0" customWidth="1"/>
@@ -501,7 +566,7 @@
     <x:col min="27" max="27" width="10.710625" style="0" customWidth="1"/>
     <x:col min="28" max="28" width="14.139196" style="0" customWidth="1"/>
     <x:col min="29" max="29" width="16.139196" style="0" customWidth="1"/>
-    <x:col min="30" max="30" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="30" max="30" width="41.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:30">
@@ -594,6 +659,94 @@
       </x:c>
       <x:c r="AD1" s="1" t="s">
         <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:30">
+      <x:c r="A2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="AD2" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:30">
+      <x:c r="A3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="AD3" s="0" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
